--- a/jogos_2024-11-21.xlsx
+++ b/jogos_2024-11-21.xlsx
@@ -1923,26 +1923,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="N12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.2</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.62</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AD12" t="n">
         <v>2.2</v>
       </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['8', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>['40']</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45617.70833333334</v>
@@ -2052,26 +2052,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['8', '90+2']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45617.70833333334</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,49 +2346,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AA15" t="n">
         <v>5.38</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['72', '81']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45617.80208333334</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,49 +2475,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
         <v>5.38</v>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['72', '81']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45617.80208333334</v>
